--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-08-18T16:19:11.866Z</t>
+    <t>2026-08-18T18:15:37.244Z</t>
   </si>
   <si>
     <t>Cooley | Global Law Firm for Innovative Companies and Investors // Cooley // Global Law Firm</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-08-18T18:15:37.244Z</t>
+    <t>2026-08-18T18:25:35.372Z</t>
   </si>
   <si>
     <t>Cooley | Global Law Firm for Innovative Companies and Investors // Cooley // Global Law Firm</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-08-18T18:25:35.372Z</t>
+    <t>2026-08-18T19:06:27.190Z</t>
   </si>
   <si>
     <t>Cooley | Global Law Firm for Innovative Companies and Investors // Cooley // Global Law Firm</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-08-18T19:06:27.190Z</t>
+    <t>2026-08-20T17:02:58.799Z</t>
   </si>
   <si>
     <t>Cooley | Global Law Firm for Innovative Companies and Investors // Cooley // Global Law Firm</t>
